--- a/CPRD Raw Analysis/Results/SecondaryCareAnalysis/OP/Output_Costs_Raw.xlsx
+++ b/CPRD Raw Analysis/Results/SecondaryCareAnalysis/OP/Output_Costs_Raw.xlsx
@@ -414,7 +414,7 @@
     </row>
     <row r="2">
       <c r="B2">
-        <v>1339.19</v>
+        <v>1339.05</v>
       </c>
       <c r="C2">
         <v>31.46</v>
@@ -423,13 +423,13 @@
         <v>77425.78</v>
       </c>
       <c r="E2">
-        <v>1750.14</v>
+        <v>1749.96</v>
       </c>
       <c r="F2">
         <v>874.6799999999999</v>
       </c>
       <c r="G2">
-        <v>490.13</v>
+        <v>489.74</v>
       </c>
       <c r="H2">
         <v>1638.42</v>
@@ -504,7 +504,7 @@
     </row>
     <row r="2">
       <c r="B2">
-        <v>1199.1</v>
+        <v>1198.98</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -513,7 +513,7 @@
         <v>77425.78</v>
       </c>
       <c r="E2">
-        <v>1706.04</v>
+        <v>1705.86</v>
       </c>
       <c r="F2">
         <v>766.33</v>
@@ -522,7 +522,7 @@
         <v>354.3</v>
       </c>
       <c r="H2">
-        <v>1506.82</v>
+        <v>1506.68</v>
       </c>
     </row>
   </sheetData>

--- a/CPRD Raw Analysis/Results/SecondaryCareAnalysis/OP/Output_Costs_Raw.xlsx
+++ b/CPRD Raw Analysis/Results/SecondaryCareAnalysis/OP/Output_Costs_Raw.xlsx
@@ -358,7 +358,7 @@
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>n_exposed</t>
+          <t>n</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -413,26 +413,38 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2">
+        <v>20691</v>
+      </c>
       <c r="B2">
-        <v>1339.05</v>
+        <v>1372.7</v>
       </c>
       <c r="C2">
-        <v>31.46</v>
+        <v>44.74</v>
       </c>
       <c r="D2">
-        <v>77425.78</v>
+        <v>56029.78</v>
       </c>
       <c r="E2">
-        <v>1749.96</v>
+        <v>1708.3</v>
       </c>
       <c r="F2">
-        <v>874.6799999999999</v>
+        <v>900.42</v>
       </c>
       <c r="G2">
-        <v>489.74</v>
+        <v>493.43</v>
       </c>
       <c r="H2">
-        <v>1638.42</v>
+        <v>1689.51</v>
+      </c>
+      <c r="I2">
+        <v>11.88</v>
+      </c>
+      <c r="J2">
+        <v>1349.42</v>
+      </c>
+      <c r="K2">
+        <v>1395.97</v>
       </c>
     </row>
   </sheetData>
@@ -448,7 +460,7 @@
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>n_exposed</t>
+          <t>n</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -503,26 +515,38 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2">
+        <v>23106</v>
+      </c>
       <c r="B2">
-        <v>1198.98</v>
+        <v>1229.11</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>77425.78</v>
+        <v>56029.78</v>
       </c>
       <c r="E2">
-        <v>1705.86</v>
+        <v>1670.18</v>
       </c>
       <c r="F2">
-        <v>766.33</v>
+        <v>792.25</v>
       </c>
       <c r="G2">
-        <v>354.3</v>
+        <v>360.31</v>
       </c>
       <c r="H2">
-        <v>1506.68</v>
+        <v>1552.7</v>
+      </c>
+      <c r="I2">
+        <v>10.99</v>
+      </c>
+      <c r="J2">
+        <v>1207.57</v>
+      </c>
+      <c r="K2">
+        <v>1250.64</v>
       </c>
     </row>
   </sheetData>

--- a/CPRD Raw Analysis/Results/SecondaryCareAnalysis/OP/Output_Costs_Raw.xlsx
+++ b/CPRD Raw Analysis/Results/SecondaryCareAnalysis/OP/Output_Costs_Raw.xlsx
@@ -417,34 +417,34 @@
         <v>20691</v>
       </c>
       <c r="B2">
-        <v>1372.7</v>
+        <v>1372.39</v>
       </c>
       <c r="C2">
-        <v>44.74</v>
+        <v>12.88</v>
       </c>
       <c r="D2">
-        <v>56029.78</v>
+        <v>39989.81</v>
       </c>
       <c r="E2">
-        <v>1708.3</v>
+        <v>1700.11</v>
       </c>
       <c r="F2">
-        <v>900.42</v>
+        <v>874.33</v>
       </c>
       <c r="G2">
-        <v>493.43</v>
+        <v>435.68</v>
       </c>
       <c r="H2">
-        <v>1689.51</v>
+        <v>1703.14</v>
       </c>
       <c r="I2">
-        <v>11.88</v>
+        <v>11.82</v>
       </c>
       <c r="J2">
-        <v>1349.42</v>
+        <v>1349.22</v>
       </c>
       <c r="K2">
-        <v>1395.97</v>
+        <v>1395.55</v>
       </c>
     </row>
   </sheetData>
@@ -519,34 +519,34 @@
         <v>23106</v>
       </c>
       <c r="B2">
-        <v>1229.11</v>
+        <v>1228.75</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>56029.78</v>
+        <v>39989.81</v>
       </c>
       <c r="E2">
-        <v>1670.18</v>
+        <v>1662.63</v>
       </c>
       <c r="F2">
-        <v>792.25</v>
+        <v>748.47</v>
       </c>
       <c r="G2">
-        <v>360.31</v>
+        <v>323.24</v>
       </c>
       <c r="H2">
-        <v>1552.7</v>
+        <v>1562.39</v>
       </c>
       <c r="I2">
-        <v>10.99</v>
+        <v>10.94</v>
       </c>
       <c r="J2">
-        <v>1207.57</v>
+        <v>1207.31</v>
       </c>
       <c r="K2">
-        <v>1250.64</v>
+        <v>1250.19</v>
       </c>
     </row>
   </sheetData>
